--- a/frontend/public/gen-sticker-docs/originals/06-uiux.xlsx
+++ b/frontend/public/gen-sticker-docs/originals/06-uiux.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Screen Flow" sheetId="1" r:id="R4bcc6eccff944c92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Docs Layout" sheetId="2" r:id="Rbfc2ce711fd048d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screens" sheetId="3" r:id="R15ef0eb361ca4498"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen Flows" sheetId="4" r:id="Rf0d3ad0dab45435d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Components" sheetId="5" r:id="R18d6dcb2ae1944d3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsive" sheetId="6" r:id="R65df3c319ff64acd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content States" sheetId="7" r:id="R57320fdd3ff54539"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="8" r:id="Rfbd5de9d8483436d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Tokens" sheetId="9" r:id="R9e44e514eaf44c32"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generation States" sheetId="10" r:id="Rd9263a9591ac4a29"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auth &amp; History" sheetId="11" r:id="R0aa7f5766f8f481a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gallery &amp; Export" sheetId="12" r:id="R1bef20b125e84a33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsive QA" sheetId="13" r:id="R3d7c62da3bec41f8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Screen Flow" sheetId="1" r:id="R9d237bd883584f35"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Visual Docs Layout" sheetId="2" r:id="Rb0e328696f4a4a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screens" sheetId="3" r:id="Rec75d2dd501649fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen Flows" sheetId="4" r:id="R6fa371bc622347bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Components" sheetId="5" r:id="Rffd724a505ee419f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsive" sheetId="6" r:id="Rca3bddb7fc554aa0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content States" sheetId="7" r:id="R792a12d1629c4400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Accessibility" sheetId="8" r:id="Rb30207d5be7143a0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Tokens" sheetId="9" r:id="Rb9d8806a0b0b4c74"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Generation States" sheetId="10" r:id="R62209860f8834915"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Auth &amp; History" sheetId="11" r:id="Ra9b39ef953974f7b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gallery &amp; Export" sheetId="12" r:id="R401d92dc73684fea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Responsive QA" sheetId="13" r:id="R8b27ea80ce1d415c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Face Gate UX" sheetId="14" r:id="R7336aa6e13654600"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -419,13 +420,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="58a09beb-530c-46c3-a660-0052a721537e"/>
+        <xdr:cNvPr id="1" name="c0ef22da-b744-4f04-8262-e55e11964e18"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rdb61c4dfec6f4df7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Rf19b5ddeb81b4bbc"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -451,13 +452,13 @@
     <xdr:ext cx="11734800" cy="6600825"/>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1" name="047df614-4c7b-4532-8548-ef6ba05d50a5"/>
+        <xdr:cNvPr id="1" name="2bb25085-cda6-40ee-a653-fefa9ccbde19"/>
         <xdr:cNvPicPr>
           <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="Ree2dc3a738e3434d"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r:embed="R049a9fa949cb46ed"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -507,6 +508,20 @@
     <x:tableColumn id="2" name="Layout"/>
     <x:tableColumn id="3" name="Critical checks"/>
     <x:tableColumn id="4" name="Status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="12" name="GS0612Table" displayName="GS0612Table" ref="A6:E13" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A6:E13"/>
+  <x:tableColumns count="5">
+    <x:tableColumn id="1" name="State"/>
+    <x:tableColumn id="2" name="Visual/copy"/>
+    <x:tableColumn id="3" name="Allowed action"/>
+    <x:tableColumn id="4" name="Accessibility"/>
+    <x:tableColumn id="5" name="Exit"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -852,7 +867,7 @@
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="7" t="str">
-        <x:v>Các view, overlay và state chuyển đổi thực tế trong frontend</x:v>
+        <x:v>Upload có preflight checking/verified; input reject tách khỏi output reject</x:v>
       </x:c>
       <x:c r="B2" s="7"/>
       <x:c r="C2" s="7"/>
@@ -904,7 +919,7 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="16" t="str">
-        <x:v>Upload nối Auth modal và Processing</x:v>
+        <x:v>Upload chuyển Face checking</x:v>
       </x:c>
       <x:c r="B8" s="16"/>
       <x:c r="C8" s="16"/>
@@ -912,7 +927,7 @@
       <x:c r="E8" s="16"/>
       <x:c r="F8" s="16"/>
       <x:c r="I8" s="22" t="str">
-        <x:v>kết quả sang Gallery hoặc Rejected</x:v>
+        <x:v>invalid quay về Upload với alert, verified mới đi Auth hoặc Processing</x:v>
       </x:c>
       <x:c r="J8" s="22"/>
       <x:c r="K8" s="22"/>
@@ -998,7 +1013,7 @@
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="28" t="str">
-        <x:v>Gallery mở History/Telegram</x:v>
+        <x:v>các nhánh Gallery, Rejected, History, Telegram và Docs giữ nguyên</x:v>
       </x:c>
       <x:c r="B18" s="28"/>
       <x:c r="C18" s="28"/>
@@ -1006,7 +1021,7 @@
       <x:c r="E18" s="28"/>
       <x:c r="F18" s="28"/>
       <x:c r="I18" s="34" t="str">
-        <x:v>header mở Docs hub</x:v>
+        <x:v>Screen flow bổ sung trạng thái kiểm tra khuôn mặt giữa Upload và Auth/Processing.</x:v>
       </x:c>
       <x:c r="J18" s="34"/>
       <x:c r="K18" s="34"/>
@@ -1092,7 +1107,7 @@
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="43" t="str">
-        <x:v>Các view, overlay và state chuyển đổi thực tế trong frontend
+        <x:v>Upload có preflight checking/verified; input reject tách khỏi output reject
 Implemented  •  Inferred  •  Gap/Risk  •  Recommended</x:v>
       </x:c>
       <x:c r="B28" s="43"/>
@@ -1175,7 +1190,7 @@
     </x:row>
     <x:row r="42" ht="34" customHeight="1">
       <x:c r="A42" s="45" t="str">
-        <x:v>Hình GS-DOC-06 — Screen flow của web app. Bản đồ view, overlay và chuyển trạng thái chính của ứng dụng web.</x:v>
+        <x:v>Hình GS-DOC-06 — Screen flow của web app. Screen flow bổ sung trạng thái kiểm tra khuôn mặt giữa Upload và Auth/Processing.</x:v>
       </x:c>
       <x:c r="B42" s="45"/>
       <x:c r="C42" s="45"/>
@@ -1193,7 +1208,7 @@
     </x:row>
     <x:row r="44" ht="42" customHeight="1">
       <x:c r="A44" s="49" t="str">
-        <x:v>Mô tả sơ đồ: Upload nối Auth modal và Processing; kết quả sang Gallery hoặc Rejected; Gallery mở History/Telegram; header mở Docs hub.</x:v>
+        <x:v>Mô tả sơ đồ: Upload chuyển Face checking; invalid quay về Upload với alert, verified mới đi Auth hoặc Processing; các nhánh Gallery, Rejected, History, Telegram và Docs giữ nguyên.</x:v>
       </x:c>
       <x:c r="B44" s="49"/>
       <x:c r="C44" s="49"/>
@@ -1211,7 +1226,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: frontend/src/App.tsx; frontend/src/components; frontend/src/hooks/useStickerGenerator.ts  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/src/components/upload/ImageUploader.tsx; frontend/src/hooks/useImageUpload.ts; frontend/src/App.tsx  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -1246,7 +1261,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R33166192db994d3e"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e4194c5e1314de2"/>
 </x:worksheet>
 </file>
 
@@ -1281,7 +1296,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1408,7 +1423,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1fd460d679d40a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd1f0f6d9060d4338"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1444,7 +1459,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1554,7 +1569,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra97198a210524d98"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra03fddcee63c4e8f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1590,7 +1605,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1700,7 +1715,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2cd803c6681f40eb"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R69276b6a147d4654"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1733,7 +1748,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -1840,7 +1855,204 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf23cd318124f48ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb8101f89b49d40bf"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="14" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="25" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="14" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="38" customHeight="1">
+      <x:c r="A1" s="53" t="str">
+        <x:v>06  /  UI/UX Specification &amp; Screen Flow</x:v>
+      </x:c>
+      <x:c r="B1" s="53"/>
+      <x:c r="C1" s="53"/>
+      <x:c r="D1" s="53"/>
+      <x:c r="E1" s="53"/>
+    </x:row>
+    <x:row r="2" ht="30" customHeight="1">
+      <x:c r="A2" s="56" t="str">
+        <x:v>Upload states, copy, accessibility và responsive behavior cho detector local</x:v>
+      </x:c>
+      <x:c r="B2" s="56"/>
+      <x:c r="C2" s="56"/>
+      <x:c r="D2" s="56"/>
+      <x:c r="E2" s="56"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="57" t="str">
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
+      </x:c>
+      <x:c r="B3" s="57"/>
+      <x:c r="C3" s="57"/>
+      <x:c r="D3" s="57"/>
+      <x:c r="E3" s="57"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="58" t="str">
+        <x:v>AS-BUILT • Nội dung viết từ source hiện tại; bộ mẫu chỉ cung cấp cấu trúc trình bày.</x:v>
+      </x:c>
+      <x:c r="B4" s="58"/>
+      <x:c r="C4" s="58"/>
+      <x:c r="D4" s="58"/>
+      <x:c r="E4" s="58"/>
+    </x:row>
+    <x:row r="6" ht="30" customHeight="1">
+      <x:c r="A6" s="64" t="str">
+        <x:v>State</x:v>
+      </x:c>
+      <x:c r="B6" s="64" t="str">
+        <x:v>Visual/copy</x:v>
+      </x:c>
+      <x:c r="C6" s="64" t="str">
+        <x:v>Allowed action</x:v>
+      </x:c>
+      <x:c r="D6" s="64" t="str">
+        <x:v>Accessibility</x:v>
+      </x:c>
+      <x:c r="E6" s="64" t="str">
+        <x:v>Exit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A7" s="69" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+      <x:c r="B7" s="69" t="str">
+        <x:v>Chọn ảnh chân dung đúng một khuôn mặt</x:v>
+      </x:c>
+      <x:c r="C7" s="69" t="str">
+        <x:v>Picker/drop/style</x:v>
+      </x:c>
+      <x:c r="D7" s="69" t="str">
+        <x:v>Keyboard upload control</x:v>
+      </x:c>
+      <x:c r="E7" s="69" t="str">
+        <x:v>checking</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A8" s="70" t="str">
+        <x:v>checking</x:v>
+      </x:c>
+      <x:c r="B8" s="70" t="str">
+        <x:v>Spinner + filename + local/privacy note</x:v>
+      </x:c>
+      <x:c r="C8" s="70" t="str">
+        <x:v>Upload/style/generate locked</x:v>
+      </x:c>
+      <x:c r="D8" s="70" t="str">
+        <x:v>aria-busy + live status</x:v>
+      </x:c>
+      <x:c r="E8" s="70" t="str">
+        <x:v>verified/error</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="43.20000076293945" hidden="0" customHeight="1">
+      <x:c r="A9" s="69" t="str">
+        <x:v>verified</x:v>
+      </x:c>
+      <x:c r="B9" s="69" t="str">
+        <x:v>Green shield + filename/size</x:v>
+      </x:c>
+      <x:c r="C9" s="69" t="str">
+        <x:v>Generate or clear</x:v>
+      </x:c>
+      <x:c r="D9" s="69" t="str">
+        <x:v>Text + icon, not color only</x:v>
+      </x:c>
+      <x:c r="E9" s="69" t="str">
+        <x:v>processing/idle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A10" s="70" t="str">
+        <x:v>0 face</x:v>
+      </x:c>
+      <x:c r="B10" s="70" t="str">
+        <x:v>Không tìm thấy khuôn mặt</x:v>
+      </x:c>
+      <x:c r="C10" s="70" t="str">
+        <x:v>Chọn lại</x:v>
+      </x:c>
+      <x:c r="D10" s="70" t="str">
+        <x:v>role=alert</x:v>
+      </x:c>
+      <x:c r="E10" s="70" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="21.600000381469727" hidden="0" customHeight="1">
+      <x:c r="A11" s="69" t="str">
+        <x:v>&gt;1 face</x:v>
+      </x:c>
+      <x:c r="B11" s="69" t="str">
+        <x:v>Báo số khuôn mặt</x:v>
+      </x:c>
+      <x:c r="C11" s="69" t="str">
+        <x:v>Chọn lại</x:v>
+      </x:c>
+      <x:c r="D11" s="69" t="str">
+        <x:v>role=alert</x:v>
+      </x:c>
+      <x:c r="E11" s="69" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A12" s="70" t="str">
+        <x:v>runtime error</x:v>
+      </x:c>
+      <x:c r="B12" s="70" t="str">
+        <x:v>Không thể kiểm tra; reload/retry</x:v>
+      </x:c>
+      <x:c r="C12" s="70" t="str">
+        <x:v>Không Generate</x:v>
+      </x:c>
+      <x:c r="D12" s="70" t="str">
+        <x:v>assertive error</x:v>
+      </x:c>
+      <x:c r="E12" s="70" t="str">
+        <x:v>idle</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="32.400001525878906" hidden="0" customHeight="1">
+      <x:c r="A13" s="69" t="str">
+        <x:v>responsive</x:v>
+      </x:c>
+      <x:c r="B13" s="69" t="str">
+        <x:v>Filename/message wrap</x:v>
+      </x:c>
+      <x:c r="C13" s="69" t="str">
+        <x:v>Touch upload</x:v>
+      </x:c>
+      <x:c r="D13" s="69" t="str">
+        <x:v>No horizontal overflow</x:v>
+      </x:c>
+      <x:c r="E13" s="69" t="str">
+        <x:v>375/390 QA</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:E1"/>
+    <x:mergeCell ref="A2:E2"/>
+    <x:mergeCell ref="A3:E3"/>
+    <x:mergeCell ref="A4:E4"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb279a398295b4b82"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2247,7 +2459,7 @@
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="51" t="str">
-        <x:v>Nguồn: frontend/src/components/docs/DocumentationPage.tsx; frontend/src/components/docs/DocumentationPage.css  •  kien_v5 @ c09e26a  •  2026-08-09</x:v>
+        <x:v>Nguồn: frontend/src/components/docs/DocumentationPage.tsx; frontend/src/components/docs/DocumentationPage.css  •  kien_v5 @ 4d23b9a  •  2026-08-10</x:v>
       </x:c>
       <x:c r="B46" s="51"/>
       <x:c r="C46" s="51"/>
@@ -2282,7 +2494,7 @@
   <x:printOptions horizontalCentered="1"/>
   <x:pageMargins left="0.25" right="0.25" top="0.4" bottom="0.4" header="0.2" footer="0.2"/>
   <x:pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf20892d298be4379"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1105c01f6b0f4685"/>
 </x:worksheet>
 </file>
 
@@ -2317,7 +2529,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2478,7 +2690,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfaaa162f923c4f83"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R892563e0cb3d4d5d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2514,7 +2726,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2675,7 +2887,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8848f583db13478e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4d30d57471c847fd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2711,7 +2923,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2838,7 +3050,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8fc91c8f460446e7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R82ade15e04714cc1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2868,7 +3080,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -2966,7 +3178,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf179798d07dd4cba"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfcc7eba7cb764ccb"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2999,7 +3211,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3106,7 +3318,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca9f939cc52d4bd9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7be510d2a1fa4247"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3136,7 +3348,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3234,7 +3446,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98e3cdea9b814e15"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R89dbb2cfd4834664"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3267,7 +3479,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="57" t="str">
-        <x:v>GS-DOC-06  •  kien_v5 @ c09e26a  •  2026-08-09  •  Current + docs view</x:v>
+        <x:v>GS-DOC-06  •  kien_v5 @ 4d23b9a  •  2026-08-10  •  Current + docs view</x:v>
       </x:c>
       <x:c r="B3" s="57"/>
       <x:c r="C3" s="57"/>
@@ -3388,7 +3600,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4f8adb90f6804c0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc592298a0e014d93"/>
   </x:tableParts>
 </x:worksheet>
 </file>